--- a/docs/version 3.xlsx
+++ b/docs/version 3.xlsx
@@ -2337,27 +2337,27 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Which of the following numbers is different?</t>
+          <t>Which pair does NOT match?</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>987564</t>
+          <t>987654  /  987564</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>987654</t>
+          <t>456789  /  456789</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>987654</t>
+          <t>123456  /  123456</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>987654</t>
+          <t>987654  /  987654</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
